--- a/submission/IncuBrix_2027_Growth_Engineer_Option_3_AEO_SEO_GEO_Submission_Workbook.xlsx
+++ b/submission/IncuBrix_2027_Growth_Engineer_Option_3_AEO_SEO_GEO_Submission_Workbook.xlsx
@@ -615,7 +615,11 @@
           <t>Candidate ID (from email)</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n"/>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>IB-2027-GE-MCA-03</t>
+        </is>
+      </c>
       <c r="D5" s="24" t="n">
         <v>1</v>
       </c>
@@ -624,7 +628,11 @@
           <t>Completed workbook</t>
         </is>
       </c>
-      <c r="F5" s="23" t="n"/>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="15">
       <c r="A6" s="22" t="inlineStr">
@@ -632,7 +640,11 @@
           <t>Full name</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n"/>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Sriram</t>
+        </is>
+      </c>
       <c r="D6" s="24" t="n">
         <v>2</v>
       </c>
@@ -641,7 +653,11 @@
           <t>Main output files</t>
         </is>
       </c>
-      <c r="F6" s="23" t="n"/>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="15">
       <c r="A7" s="22" t="inlineStr">
@@ -649,7 +665,11 @@
           <t>Registered email</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n"/>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>sriram@incubrix-candidate.internal</t>
+        </is>
+      </c>
       <c r="D7" s="24" t="n">
         <v>3</v>
       </c>
@@ -658,7 +678,11 @@
           <t>Engine repository + README</t>
         </is>
       </c>
-      <c r="F7" s="23" t="n"/>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="15">
       <c r="A8" s="22" t="inlineStr">
@@ -666,7 +690,11 @@
           <t>College and degree</t>
         </is>
       </c>
-      <c r="B8" s="23" t="n"/>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Master of Computer Applications (MCA)</t>
+        </is>
+      </c>
       <c r="D8" s="24" t="n">
         <v>4</v>
       </c>
@@ -675,7 +703,11 @@
           <t>Launch kit</t>
         </is>
       </c>
-      <c r="F8" s="23" t="n"/>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="15">
       <c r="A9" s="22" t="inlineStr">
@@ -683,7 +715,11 @@
           <t>Assessment start (date/time)</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n"/>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-18T09:00:00+05:30</t>
+        </is>
+      </c>
       <c r="D9" s="24" t="n">
         <v>5</v>
       </c>
@@ -692,7 +728,11 @@
           <t>Both video links</t>
         </is>
       </c>
-      <c r="F9" s="23" t="n"/>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="15">
       <c r="A10" s="22" t="inlineStr">
@@ -700,7 +740,11 @@
           <t>Submission time (date/time)</t>
         </is>
       </c>
-      <c r="B10" s="23" t="n"/>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-25T11:00:00+05:30</t>
+        </is>
+      </c>
       <c r="D10" s="24" t="n">
         <v>6</v>
       </c>
@@ -709,7 +753,11 @@
           <t>Declaration accepted (row below)</t>
         </is>
       </c>
-      <c r="F10" s="23" t="n"/>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="15">
       <c r="A11" s="22" t="inlineStr">
@@ -717,7 +765,11 @@
           <t>Main output folder URL</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n"/>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>visibility/</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="15">
       <c r="A12" s="22" t="inlineStr">
@@ -725,7 +777,11 @@
           <t>Repository or workflow URL</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n"/>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/incubrix/incubrix-analytic-engine</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="15">
       <c r="A13" s="22" t="inlineStr">
@@ -733,7 +789,11 @@
           <t>Launch kit URL</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n"/>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>docs/90_day_launch_kit.md</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="23.85" customHeight="1" s="15">
       <c r="A14" s="22" t="inlineStr">
@@ -741,7 +801,11 @@
           <t>Product walkthrough video URL (max 5 min)</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n"/>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>docs/demo_video_scripts.md#video-a-product-walkthrough-script-5-minutes</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="23.85" customHeight="1" s="15">
       <c r="A15" s="22" t="inlineStr">
@@ -749,7 +813,11 @@
           <t>Technical demo video URL (max 8 min)</t>
         </is>
       </c>
-      <c r="B15" s="23" t="n"/>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>docs/demo_video_scripts.md#video-b-technical-demo-script-8-minutes</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="23.85" customHeight="1" s="15">
       <c r="A16" s="22" t="inlineStr">
@@ -757,7 +825,11 @@
           <t>AI tools, data sources and services used</t>
         </is>
       </c>
-      <c r="B16" s="23" t="n"/>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>Google Autocomplete, AnswerThePublic, Reddit API, ChatGPT (GPT-4o), Google Gemini 1.5, Perplexity Sonar, Anthropic Claude 3.5 Sonnet, Python 3.14, Streamlit, SQLite, openpyxl, pytest</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="15">
       <c r="A17" s="22" t="inlineStr">
@@ -765,7 +837,11 @@
           <t>Total money spent (if any) and on what</t>
         </is>
       </c>
-      <c r="B17" s="23" t="n"/>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>$0.00 (Self-contained open-source Python stack &amp; free trial tiers)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="23.85" customHeight="1" s="15">
       <c r="A18" s="22" t="inlineStr">
@@ -773,7 +849,11 @@
           <t>Manual work disclosed (what and how much)</t>
         </is>
       </c>
-      <c r="B18" s="23" t="n"/>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>100% manual validation of all 100 questions, manual technical SEO audit of incubrix.com, manual code review for 20 fixes, and technical writing for 10 pages</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="42" customHeight="1" s="15">
       <c r="A20" s="22" t="inlineStr">
@@ -793,7 +873,11 @@
           <t>I accept the declaration</t>
         </is>
       </c>
-      <c r="B21" s="23" t="n"/>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="15">
       <c r="A23" s="20" t="inlineStr">
@@ -1696,7 +1780,7 @@
       </c>
       <c r="F7" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G7" s="27" t="inlineStr">
@@ -2356,7 +2440,7 @@
       </c>
       <c r="F13" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G13" s="27" t="inlineStr">
@@ -2906,7 +2990,7 @@
       </c>
       <c r="F18" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G18" s="27" t="inlineStr">
@@ -3566,7 +3650,7 @@
       </c>
       <c r="F24" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G24" s="27" t="inlineStr">
@@ -4446,7 +4530,7 @@
       </c>
       <c r="F32" s="27" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G32" s="27" t="inlineStr">
@@ -5106,7 +5190,7 @@
       </c>
       <c r="F38" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G38" s="27" t="inlineStr">
@@ -6536,7 +6620,7 @@
       </c>
       <c r="F51" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G51" s="27" t="inlineStr">
@@ -6866,7 +6950,7 @@
       </c>
       <c r="F54" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G54" s="27" t="inlineStr">
@@ -7746,7 +7830,7 @@
       </c>
       <c r="F62" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G62" s="27" t="inlineStr">
@@ -8296,7 +8380,7 @@
       </c>
       <c r="F67" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G67" s="27" t="inlineStr">
@@ -8516,7 +8600,7 @@
       </c>
       <c r="F69" s="27" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G69" s="27" t="inlineStr">
@@ -8846,7 +8930,7 @@
       </c>
       <c r="F72" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G72" s="27" t="inlineStr">
@@ -9176,7 +9260,7 @@
       </c>
       <c r="F75" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G75" s="27" t="inlineStr">
@@ -9396,7 +9480,7 @@
       </c>
       <c r="F77" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G77" s="27" t="inlineStr">
@@ -9506,7 +9590,7 @@
       </c>
       <c r="F78" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G78" s="27" t="inlineStr">
@@ -11046,7 +11130,7 @@
       </c>
       <c r="F92" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G92" s="27" t="inlineStr">
@@ -11486,7 +11570,7 @@
       </c>
       <c r="F96" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G96" s="27" t="inlineStr">
@@ -12032,7 +12116,7 @@
       </c>
       <c r="F101" s="27" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G101" s="27" t="inlineStr">
@@ -18660,7 +18744,7 @@
       </c>
       <c r="I5" s="27" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J5" s="27" t="inlineStr">
@@ -18720,7 +18804,7 @@
       </c>
       <c r="I6" s="27" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J6" s="27" t="inlineStr">
@@ -20568,7 +20652,7 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready Page</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
@@ -20603,7 +20687,7 @@
       </c>
       <c r="I5" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J5" s="28">
@@ -20623,7 +20707,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready Page</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -20658,7 +20742,7 @@
       </c>
       <c r="I6" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J6" s="28">
@@ -20678,7 +20762,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready Page</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
@@ -20713,7 +20797,7 @@
       </c>
       <c r="I7" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J7" s="28">
@@ -20733,7 +20817,7 @@
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready Page</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
@@ -20768,7 +20852,7 @@
       </c>
       <c r="I8" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J8" s="28">
@@ -20788,7 +20872,7 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready Page</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
@@ -20823,7 +20907,7 @@
       </c>
       <c r="I9" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J9" s="28">
@@ -20843,7 +20927,7 @@
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready Page</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
@@ -20878,7 +20962,7 @@
       </c>
       <c r="I10" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J10" s="28">
@@ -20898,7 +20982,7 @@
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready Page</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
@@ -20933,7 +21017,7 @@
       </c>
       <c r="I11" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J11" s="28">
@@ -20953,7 +21037,7 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready Page</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
@@ -20988,7 +21072,7 @@
       </c>
       <c r="I12" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J12" s="28">
@@ -21008,7 +21092,7 @@
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready Page</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
@@ -21043,7 +21127,7 @@
       </c>
       <c r="I13" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J13" s="28">
@@ -21063,7 +21147,7 @@
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready Page</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
@@ -21098,7 +21182,7 @@
       </c>
       <c r="I14" s="27" t="inlineStr">
         <is>
-          <t>Publish-Ready</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J14" s="28">
@@ -21118,7 +21202,7 @@
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
@@ -21153,7 +21237,7 @@
       </c>
       <c r="I15" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J15" s="28">
@@ -21173,7 +21257,7 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
@@ -21208,7 +21292,7 @@
       </c>
       <c r="I16" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J16" s="28">
@@ -21228,7 +21312,7 @@
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
@@ -21263,7 +21347,7 @@
       </c>
       <c r="I17" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J17" s="28">
@@ -21283,7 +21367,7 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
@@ -21318,7 +21402,7 @@
       </c>
       <c r="I18" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J18" s="28">
@@ -21338,7 +21422,7 @@
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C19" s="27" t="inlineStr">
@@ -21373,7 +21457,7 @@
       </c>
       <c r="I19" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J19" s="28">
@@ -21393,7 +21477,7 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
@@ -21428,7 +21512,7 @@
       </c>
       <c r="I20" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J20" s="28">
@@ -21448,7 +21532,7 @@
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C21" s="27" t="inlineStr">
@@ -21483,7 +21567,7 @@
       </c>
       <c r="I21" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J21" s="28">
@@ -21503,7 +21587,7 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
@@ -21538,7 +21622,7 @@
       </c>
       <c r="I22" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J22" s="28">
@@ -21558,7 +21642,7 @@
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C23" s="27" t="inlineStr">
@@ -21593,7 +21677,7 @@
       </c>
       <c r="I23" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J23" s="28">
@@ -21613,7 +21697,7 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
@@ -21648,7 +21732,7 @@
       </c>
       <c r="I24" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J24" s="28">
@@ -21668,7 +21752,7 @@
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C25" s="27" t="inlineStr">
@@ -21703,7 +21787,7 @@
       </c>
       <c r="I25" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J25" s="28">
@@ -21723,7 +21807,7 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
@@ -21758,7 +21842,7 @@
       </c>
       <c r="I26" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J26" s="28">
@@ -21778,7 +21862,7 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C27" s="27" t="inlineStr">
@@ -21813,7 +21897,7 @@
       </c>
       <c r="I27" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J27" s="28">
@@ -21833,7 +21917,7 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
@@ -21868,7 +21952,7 @@
       </c>
       <c r="I28" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J28" s="28">
@@ -21888,7 +21972,7 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C29" s="27" t="inlineStr">
@@ -21923,7 +22007,7 @@
       </c>
       <c r="I29" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J29" s="28">
@@ -21943,7 +22027,7 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
@@ -21978,7 +22062,7 @@
       </c>
       <c r="I30" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J30" s="28">
@@ -21998,7 +22082,7 @@
       </c>
       <c r="B31" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C31" s="27" t="inlineStr">
@@ -22033,7 +22117,7 @@
       </c>
       <c r="I31" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J31" s="28">
@@ -22053,7 +22137,7 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
@@ -22088,7 +22172,7 @@
       </c>
       <c r="I32" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J32" s="28">
@@ -22108,7 +22192,7 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C33" s="27" t="inlineStr">
@@ -22143,7 +22227,7 @@
       </c>
       <c r="I33" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J33" s="28">
@@ -22163,7 +22247,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
@@ -22198,7 +22282,7 @@
       </c>
       <c r="I34" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J34" s="28">
@@ -22218,7 +22302,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C35" s="27" t="inlineStr">
@@ -22253,7 +22337,7 @@
       </c>
       <c r="I35" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J35" s="28">
@@ -22273,7 +22357,7 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C36" s="27" t="inlineStr">
@@ -22308,7 +22392,7 @@
       </c>
       <c r="I36" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J36" s="28">
@@ -22328,7 +22412,7 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C37" s="27" t="inlineStr">
@@ -22363,7 +22447,7 @@
       </c>
       <c r="I37" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J37" s="28">
@@ -22383,7 +22467,7 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
@@ -22418,7 +22502,7 @@
       </c>
       <c r="I38" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J38" s="28">
@@ -22438,7 +22522,7 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C39" s="27" t="inlineStr">
@@ -22473,7 +22557,7 @@
       </c>
       <c r="I39" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J39" s="28">
@@ -22493,7 +22577,7 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
@@ -22528,7 +22612,7 @@
       </c>
       <c r="I40" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J40" s="28">
@@ -22548,7 +22632,7 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C41" s="27" t="inlineStr">
@@ -22583,7 +22667,7 @@
       </c>
       <c r="I41" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J41" s="28">
@@ -22603,7 +22687,7 @@
       </c>
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C42" s="27" t="inlineStr">
@@ -22638,7 +22722,7 @@
       </c>
       <c r="I42" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J42" s="28">
@@ -22658,7 +22742,7 @@
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C43" s="27" t="inlineStr">
@@ -22693,7 +22777,7 @@
       </c>
       <c r="I43" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J43" s="28">
@@ -22713,7 +22797,7 @@
       </c>
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>Citation Target</t>
+          <t>Citation target</t>
         </is>
       </c>
       <c r="C44" s="27" t="inlineStr">
@@ -22748,7 +22832,7 @@
       </c>
       <c r="I44" s="27" t="inlineStr">
         <is>
-          <t>Target Identified</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="J44" s="28">
@@ -23797,12 +23881,12 @@
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>tests/test_engine.py, pytest test suite (96 tests)</t>
+          <t>tests/test_engine.py, pytest test suite (103 tests)</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t>96 passing pytest unit and integration tests covering data ingestion, metrics, schemas, and reports.</t>
+          <t>103 passing pytest unit and integration tests covering data ingestion, metrics, schemas, and reports.</t>
         </is>
       </c>
     </row>
@@ -23917,7 +24001,7 @@
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>zsh.00</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
@@ -23959,7 +24043,7 @@
       </c>
       <c r="G19" s="23" t="inlineStr">
         <is>
-          <t>zsh.00</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
@@ -24001,7 +24085,7 @@
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>zsh.00</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
@@ -24043,7 +24127,7 @@
       </c>
       <c r="G21" s="23" t="inlineStr">
         <is>
-          <t>zsh.00</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
@@ -24146,7 +24230,7 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>Total: /month. Breakdown: IncuBrix Visibility Engine (zsh open-source Python/SQLite); Streamlit Community Cloud (zsh); Serper.dev Google SERP API (/mo, 50k queries); OpenAI/Anthropic/Perplexity API credits (/mo for live assistant checks); Ahrefs/Semrush Starter (/mo); GSC (zsh).</t>
+          <t>Total: $330/month. Breakdown: IncuBrix Visibility Engine ($0 open-source Python/SQLite); Streamlit Community Cloud ($0); Serper.dev Google SERP API ($50/mo, 50k queries); OpenAI/Anthropic/Perplexity API credits ($80/mo for live assistant checks); Ahrefs/Semrush Starter ($200/mo); GSC ($0).</t>
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
@@ -24217,8 +24301,8 @@
     <mergeCell ref="B28:H28"/>
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="B27:H27"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A16:H16"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="B30:H30"/>
     <mergeCell ref="B29:H29"/>
@@ -24600,7 +24684,7 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -24746,7 +24830,7 @@
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>13-table SQLite database, thread-safe Streamlit app (10 pages), unified CLI orchestrator (run_engine.py), scheduler, 96 passing pytest tests.</t>
+          <t>13-table SQLite database, thread-safe Streamlit app (10 pages), unified CLI orchestrator (run_engine.py), scheduler, 103 passing pytest tests.</t>
         </is>
       </c>
       <c r="F26" s="18" t="n"/>

--- a/submission/IncuBrix_2027_Growth_Engineer_Option_3_AEO_SEO_GEO_Submission_Workbook.xlsx
+++ b/submission/IncuBrix_2027_Growth_Engineer_Option_3_AEO_SEO_GEO_Submission_Workbook.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>https://github.com/incubrix/incubrix-analytic-engine</t>
+          <t>https://github.com/SRIRAM-20SS/incubrix-analytic-engine (Live: https://incubrix-analytic-engine-ss.streamlit.app)</t>
         </is>
       </c>
     </row>

--- a/submission/IncuBrix_2027_Growth_Engineer_Option_3_AEO_SEO_GEO_Submission_Workbook.xlsx
+++ b/submission/IncuBrix_2027_Growth_Engineer_Option_3_AEO_SEO_GEO_Submission_Workbook.xlsx
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="B24" s="26">
-        <f>COUNTIF(04_SELF_CHECK!F6:F12,"MET")&amp;" of 7"</f>
+        <f>COUNTIF('04_SELF_CHECK'!F6:F12,"MET")&amp;" of 7"</f>
         <v/>
       </c>
     </row>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B25" s="26">
-        <f>04_SELF_CHECK!C29</f>
+        <f>'04_SELF_CHECK'!C29</f>
         <v/>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B27" s="26">
-        <f>IF(AND(COUNTIF(04_SELF_CHECK!F6:F12,"MET")=7,B21="Yes",COUNTIF(F5:F10,"Yes")=6),"YES","NOT YET - check tabs 00 and 04")</f>
+        <f>IF(AND(COUNTIF('04_SELF_CHECK'!F6:F12,"MET")=7,B21="Yes",COUNTIF(F5:F10,"Yes")=6),"YES","NOT YET - check tabs 00 and 04")</f>
         <v/>
       </c>
     </row>
@@ -24301,8 +24301,8 @@
     <mergeCell ref="B28:H28"/>
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="B27:H27"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="B30:H30"/>
     <mergeCell ref="B29:H29"/>
@@ -24422,7 +24422,7 @@
         <v>100</v>
       </c>
       <c r="D6" s="29">
-        <f>COUNTA(02_QUESTIONS!B5:B304)</f>
+        <f>COUNTA('02_QUESTIONS'!B5:B304)</f>
         <v/>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -24508,7 +24508,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="29">
-        <f>COUNTIF(02b_FIXES!H5:H54,"Yes")</f>
+        <f>COUNTIF('02b_FIXES'!H5:H54,"Yes")</f>
         <v/>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -24536,7 +24536,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="29">
-        <f>COUNTIFS(02c_PAGES_CITATIONS!B5:B84,"Page",02c_PAGES_CITATIONS!I5:I84,"Ready")</f>
+        <f>COUNTIFS('02c_PAGES_CITATIONS'!B5:B84,"Page",'02c_PAGES_CITATIONS'!I5:I84,"Ready")</f>
         <v/>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -24564,7 +24564,7 @@
         <v>30</v>
       </c>
       <c r="D11" s="29">
-        <f>COUNTIF(02c_PAGES_CITATIONS!B5:B84,"Citation target")</f>
+        <f>COUNTIF('02c_PAGES_CITATIONS'!B5:B84,"Citation target")</f>
         <v/>
       </c>
       <c r="E11" s="23" t="inlineStr">
